--- a/Data/IceStation3c/17aug2025coring_melt_ponds/20250817-PS149_41-1-SI_corer_9cm-020-SYI-SSL_melt_pond-RHO-TXT.xlsx
+++ b/Data/IceStation3c/17aug2025coring_melt_ponds/20250817-PS149_41-1-SI_corer_9cm-020-SYI-SSL_melt_pond-RHO-TXT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evsalg001\Documents\MATLAB\Contrasts coring\Data\IceStation3c\17aug2025coring_melt_ponds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236611DB-E3AC-465C-A495-193EE73A66A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64DF52CE-4CB1-4EAF-B654-5DB597AA566F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="726" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="726" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata-core" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <sheet name="CT" sheetId="12" r:id="rId12"/>
     <sheet name="lists" sheetId="13" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1704,6 +1704,18 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1713,22 +1725,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1737,7 +1734,7 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1746,17 +1743,20 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -23924,14 +23924,14 @@
       <c r="G1" s="58" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="159" t="s">
+      <c r="H1" s="158" t="s">
         <v>89</v>
       </c>
-      <c r="I1" s="159"/>
-      <c r="J1" s="159" t="s">
+      <c r="I1" s="158"/>
+      <c r="J1" s="158" t="s">
         <v>90</v>
       </c>
-      <c r="K1" s="159"/>
+      <c r="K1" s="158"/>
       <c r="L1" s="60"/>
       <c r="M1" s="58" t="s">
         <v>92</v>
@@ -23942,10 +23942,10 @@
       </c>
       <c r="P1" s="19"/>
       <c r="Q1" s="9"/>
-      <c r="R1" s="163" t="s">
+      <c r="R1" s="161" t="s">
         <v>119</v>
       </c>
-      <c r="S1" s="163"/>
+      <c r="S1" s="161"/>
       <c r="T1" s="9"/>
       <c r="U1" s="58" t="s">
         <v>82</v>
@@ -28300,11 +28300,11 @@
         <v>18</v>
       </c>
       <c r="B3" s="24"/>
-      <c r="C3" s="151" t="s">
+      <c r="C3" s="147" t="s">
         <v>294</v>
       </c>
-      <c r="D3" s="151"/>
-      <c r="E3" s="151"/>
+      <c r="D3" s="147"/>
+      <c r="E3" s="147"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -28331,11 +28331,11 @@
         <v>19</v>
       </c>
       <c r="B4" s="26"/>
-      <c r="C4" s="152" t="s">
+      <c r="C4" s="148" t="s">
         <v>307</v>
       </c>
-      <c r="D4" s="152"/>
-      <c r="E4" s="152"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -28389,11 +28389,11 @@
     <row r="6" spans="1:25" ht="13.5" customHeight="1">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="153" t="s">
+      <c r="C6" s="149" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="153"/>
-      <c r="E6" s="153"/>
+      <c r="D6" s="149"/>
+      <c r="E6" s="149"/>
       <c r="F6" s="146" t="s">
         <v>22</v>
       </c>
@@ -28464,7 +28464,8 @@
         <v>27</v>
       </c>
       <c r="C8">
-        <v>82</v>
+        <f>82+D8/60</f>
+        <v>82.95079166666666</v>
       </c>
       <c r="D8" s="30">
         <v>57.047499999999999</v>
@@ -28498,7 +28499,8 @@
         <v>29</v>
       </c>
       <c r="C9">
-        <v>-12</v>
+        <f>-12-D9/60</f>
+        <v>-12.814385</v>
       </c>
       <c r="D9" s="34">
         <v>48.863100000000003</v>
@@ -29265,11 +29267,11 @@
         <v>64</v>
       </c>
       <c r="B33" s="53"/>
-      <c r="C33" s="147"/>
-      <c r="D33" s="147"/>
-      <c r="E33" s="147"/>
-      <c r="F33" s="147"/>
-      <c r="G33" s="147"/>
+      <c r="C33" s="151"/>
+      <c r="D33" s="151"/>
+      <c r="E33" s="151"/>
+      <c r="F33" s="151"/>
+      <c r="G33" s="151"/>
       <c r="H33" s="22"/>
       <c r="I33" s="22"/>
       <c r="J33" s="22"/>
@@ -29506,11 +29508,11 @@
       <c r="Y40" s="22"/>
     </row>
     <row r="41" spans="1:25">
-      <c r="A41" s="148" t="s">
+      <c r="A41" s="152" t="s">
         <v>76</v>
       </c>
-      <c r="B41" s="148"/>
-      <c r="C41" s="148"/>
+      <c r="B41" s="152"/>
+      <c r="C41" s="152"/>
       <c r="D41" s="22"/>
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
@@ -29535,14 +29537,14 @@
       <c r="Y41" s="22"/>
     </row>
     <row r="42" spans="1:25" ht="63.75" customHeight="1">
-      <c r="A42" s="149" t="s">
+      <c r="A42" s="153" t="s">
         <v>334</v>
       </c>
-      <c r="B42" s="149"/>
-      <c r="C42" s="149"/>
-      <c r="D42" s="149"/>
-      <c r="E42" s="149"/>
-      <c r="F42" s="149"/>
+      <c r="B42" s="153"/>
+      <c r="C42" s="153"/>
+      <c r="D42" s="153"/>
+      <c r="E42" s="153"/>
+      <c r="F42" s="153"/>
       <c r="G42" s="22"/>
       <c r="H42" s="22"/>
       <c r="I42" s="22"/>
@@ -29835,21 +29837,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="C6:E6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A42:F42"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="date" prompt="Date in international format: YYYY-MM-DD" sqref="C12:D12" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -31505,11 +31507,11 @@
       <c r="B2" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="156" t="s">
+      <c r="C2" s="155" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
       <c r="F2" s="67"/>
       <c r="G2" s="67"/>
       <c r="H2" s="67"/>
@@ -31539,11 +31541,11 @@
       <c r="B3" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="C3" s="157" t="s">
+      <c r="C3" s="156" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="157"/>
-      <c r="E3" s="157"/>
+      <c r="D3" s="156"/>
+      <c r="E3" s="156"/>
       <c r="F3" s="67"/>
       <c r="G3" s="67"/>
       <c r="H3" s="67"/>
@@ -31569,9 +31571,9 @@
     <row r="4" spans="1:26" ht="15.75">
       <c r="A4" s="69"/>
       <c r="B4" s="69"/>
-      <c r="C4" s="155"/>
-      <c r="D4" s="155"/>
-      <c r="E4" s="155"/>
+      <c r="C4" s="157"/>
+      <c r="D4" s="157"/>
+      <c r="E4" s="157"/>
       <c r="F4" s="22"/>
       <c r="G4" s="22"/>
       <c r="H4" s="22"/>
@@ -31597,9 +31599,9 @@
     <row r="5" spans="1:26" ht="15.75">
       <c r="A5" s="69"/>
       <c r="B5" s="69"/>
-      <c r="C5" s="155"/>
-      <c r="D5" s="155"/>
-      <c r="E5" s="155"/>
+      <c r="C5" s="157"/>
+      <c r="D5" s="157"/>
+      <c r="E5" s="157"/>
       <c r="F5" s="22"/>
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
@@ -31625,9 +31627,9 @@
     <row r="6" spans="1:26" ht="15.75">
       <c r="A6" s="69"/>
       <c r="B6" s="69"/>
-      <c r="C6" s="155"/>
-      <c r="D6" s="155"/>
-      <c r="E6" s="155"/>
+      <c r="C6" s="157"/>
+      <c r="D6" s="157"/>
+      <c r="E6" s="157"/>
       <c r="F6" s="22"/>
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
@@ -31653,9 +31655,9 @@
     <row r="7" spans="1:26" ht="15.75">
       <c r="A7" s="69"/>
       <c r="B7" s="69"/>
-      <c r="C7" s="155"/>
-      <c r="D7" s="155"/>
-      <c r="E7" s="155"/>
+      <c r="C7" s="157"/>
+      <c r="D7" s="157"/>
+      <c r="E7" s="157"/>
       <c r="F7" s="22"/>
       <c r="G7" s="22"/>
       <c r="H7" s="22"/>
@@ -31681,9 +31683,9 @@
     <row r="8" spans="1:26" ht="15.75">
       <c r="A8" s="69"/>
       <c r="B8" s="69"/>
-      <c r="C8" s="155"/>
-      <c r="D8" s="155"/>
-      <c r="E8" s="155"/>
+      <c r="C8" s="157"/>
+      <c r="D8" s="157"/>
+      <c r="E8" s="157"/>
       <c r="F8" s="22"/>
       <c r="G8" s="22"/>
       <c r="H8" s="22"/>
@@ -31709,9 +31711,9 @@
     <row r="9" spans="1:26" ht="15.75">
       <c r="A9" s="69"/>
       <c r="B9" s="69"/>
-      <c r="C9" s="155"/>
-      <c r="D9" s="155"/>
-      <c r="E9" s="155"/>
+      <c r="C9" s="157"/>
+      <c r="D9" s="157"/>
+      <c r="E9" s="157"/>
       <c r="F9" s="22"/>
       <c r="G9" s="22"/>
       <c r="H9" s="22"/>
@@ -31737,9 +31739,9 @@
     <row r="10" spans="1:26" ht="15.75">
       <c r="A10" s="69"/>
       <c r="B10" s="69"/>
-      <c r="C10" s="155"/>
-      <c r="D10" s="155"/>
-      <c r="E10" s="155"/>
+      <c r="C10" s="157"/>
+      <c r="D10" s="157"/>
+      <c r="E10" s="157"/>
       <c r="F10" s="22"/>
       <c r="G10" s="22"/>
       <c r="H10" s="22"/>
@@ -31765,9 +31767,9 @@
     <row r="11" spans="1:26" ht="15.75">
       <c r="A11" s="69"/>
       <c r="B11" s="69"/>
-      <c r="C11" s="155"/>
-      <c r="D11" s="155"/>
-      <c r="E11" s="155"/>
+      <c r="C11" s="157"/>
+      <c r="D11" s="157"/>
+      <c r="E11" s="157"/>
       <c r="F11" s="22"/>
       <c r="G11" s="22"/>
       <c r="H11" s="22"/>
@@ -31793,9 +31795,9 @@
     <row r="12" spans="1:26" ht="15.75">
       <c r="A12" s="69"/>
       <c r="B12" s="69"/>
-      <c r="C12" s="155"/>
-      <c r="D12" s="155"/>
-      <c r="E12" s="155"/>
+      <c r="C12" s="157"/>
+      <c r="D12" s="157"/>
+      <c r="E12" s="157"/>
       <c r="F12" s="22"/>
       <c r="G12" s="22"/>
       <c r="H12" s="22"/>
@@ -31821,9 +31823,9 @@
     <row r="13" spans="1:26" ht="15.75">
       <c r="A13" s="69"/>
       <c r="B13" s="69"/>
-      <c r="C13" s="155"/>
-      <c r="D13" s="155"/>
-      <c r="E13" s="155"/>
+      <c r="C13" s="157"/>
+      <c r="D13" s="157"/>
+      <c r="E13" s="157"/>
       <c r="F13" s="22"/>
       <c r="G13" s="22"/>
       <c r="H13" s="22"/>
@@ -31849,9 +31851,9 @@
     <row r="14" spans="1:26" ht="15.75">
       <c r="A14" s="69"/>
       <c r="B14" s="69"/>
-      <c r="C14" s="155"/>
-      <c r="D14" s="155"/>
-      <c r="E14" s="155"/>
+      <c r="C14" s="157"/>
+      <c r="D14" s="157"/>
+      <c r="E14" s="157"/>
       <c r="F14" s="22"/>
       <c r="G14" s="22"/>
       <c r="H14" s="22"/>
@@ -31877,9 +31879,9 @@
     <row r="15" spans="1:26" ht="15.75">
       <c r="A15" s="69"/>
       <c r="B15" s="69"/>
-      <c r="C15" s="155"/>
-      <c r="D15" s="155"/>
-      <c r="E15" s="155"/>
+      <c r="C15" s="157"/>
+      <c r="D15" s="157"/>
+      <c r="E15" s="157"/>
       <c r="F15" s="22"/>
       <c r="G15" s="22"/>
       <c r="H15" s="22"/>
@@ -31905,9 +31907,9 @@
     <row r="16" spans="1:26" ht="15.75">
       <c r="A16" s="69"/>
       <c r="B16" s="69"/>
-      <c r="C16" s="155"/>
-      <c r="D16" s="155"/>
-      <c r="E16" s="155"/>
+      <c r="C16" s="157"/>
+      <c r="D16" s="157"/>
+      <c r="E16" s="157"/>
       <c r="F16" s="22"/>
       <c r="G16" s="22"/>
       <c r="H16" s="22"/>
@@ -31933,9 +31935,9 @@
     <row r="17" spans="1:26" ht="15.75">
       <c r="A17" s="69"/>
       <c r="B17" s="69"/>
-      <c r="C17" s="155"/>
-      <c r="D17" s="155"/>
-      <c r="E17" s="155"/>
+      <c r="C17" s="157"/>
+      <c r="D17" s="157"/>
+      <c r="E17" s="157"/>
       <c r="F17" s="22"/>
       <c r="G17" s="22"/>
       <c r="H17" s="22"/>
@@ -31961,9 +31963,9 @@
     <row r="18" spans="1:26" ht="15.75">
       <c r="A18" s="69"/>
       <c r="B18" s="69"/>
-      <c r="C18" s="155"/>
-      <c r="D18" s="155"/>
-      <c r="E18" s="155"/>
+      <c r="C18" s="157"/>
+      <c r="D18" s="157"/>
+      <c r="E18" s="157"/>
       <c r="F18" s="22"/>
       <c r="G18" s="22"/>
       <c r="H18" s="22"/>
@@ -31989,9 +31991,9 @@
     <row r="19" spans="1:26" ht="15.75">
       <c r="A19" s="69"/>
       <c r="B19" s="69"/>
-      <c r="C19" s="155"/>
-      <c r="D19" s="155"/>
-      <c r="E19" s="155"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="157"/>
+      <c r="E19" s="157"/>
       <c r="F19" s="22"/>
       <c r="G19" s="22"/>
       <c r="H19" s="22"/>
@@ -32017,9 +32019,9 @@
     <row r="20" spans="1:26" ht="15.75">
       <c r="A20" s="69"/>
       <c r="B20" s="69"/>
-      <c r="C20" s="155"/>
-      <c r="D20" s="155"/>
-      <c r="E20" s="155"/>
+      <c r="C20" s="157"/>
+      <c r="D20" s="157"/>
+      <c r="E20" s="157"/>
       <c r="F20" s="22"/>
       <c r="G20" s="22"/>
       <c r="H20" s="22"/>
@@ -32045,9 +32047,9 @@
     <row r="21" spans="1:26" ht="15.75">
       <c r="A21" s="69"/>
       <c r="B21" s="69"/>
-      <c r="C21" s="155"/>
-      <c r="D21" s="155"/>
-      <c r="E21" s="155"/>
+      <c r="C21" s="157"/>
+      <c r="D21" s="157"/>
+      <c r="E21" s="157"/>
       <c r="F21" s="22"/>
       <c r="G21" s="22"/>
       <c r="H21" s="22"/>
@@ -32073,9 +32075,9 @@
     <row r="22" spans="1:26" ht="15.75">
       <c r="A22" s="69"/>
       <c r="B22" s="69"/>
-      <c r="C22" s="155"/>
-      <c r="D22" s="155"/>
-      <c r="E22" s="155"/>
+      <c r="C22" s="157"/>
+      <c r="D22" s="157"/>
+      <c r="E22" s="157"/>
       <c r="F22" s="22"/>
       <c r="G22" s="22"/>
       <c r="H22" s="22"/>
@@ -32101,9 +32103,9 @@
     <row r="23" spans="1:26" ht="15.75">
       <c r="A23" s="69"/>
       <c r="B23" s="69"/>
-      <c r="C23" s="155"/>
-      <c r="D23" s="155"/>
-      <c r="E23" s="155"/>
+      <c r="C23" s="157"/>
+      <c r="D23" s="157"/>
+      <c r="E23" s="157"/>
       <c r="F23" s="22"/>
       <c r="G23" s="22"/>
       <c r="H23" s="22"/>
@@ -32129,9 +32131,9 @@
     <row r="24" spans="1:26" ht="15.75">
       <c r="A24" s="69"/>
       <c r="B24" s="69"/>
-      <c r="C24" s="155"/>
-      <c r="D24" s="155"/>
-      <c r="E24" s="155"/>
+      <c r="C24" s="157"/>
+      <c r="D24" s="157"/>
+      <c r="E24" s="157"/>
       <c r="F24" s="22"/>
       <c r="G24" s="22"/>
       <c r="H24" s="22"/>
@@ -32157,9 +32159,9 @@
     <row r="25" spans="1:26" ht="15.75">
       <c r="A25" s="69"/>
       <c r="B25" s="69"/>
-      <c r="C25" s="155"/>
-      <c r="D25" s="155"/>
-      <c r="E25" s="155"/>
+      <c r="C25" s="157"/>
+      <c r="D25" s="157"/>
+      <c r="E25" s="157"/>
       <c r="F25" s="22"/>
       <c r="G25" s="22"/>
       <c r="H25" s="22"/>
@@ -32185,9 +32187,9 @@
     <row r="26" spans="1:26" ht="15.75">
       <c r="A26" s="69"/>
       <c r="B26" s="69"/>
-      <c r="C26" s="155"/>
-      <c r="D26" s="155"/>
-      <c r="E26" s="155"/>
+      <c r="C26" s="157"/>
+      <c r="D26" s="157"/>
+      <c r="E26" s="157"/>
       <c r="F26" s="22"/>
       <c r="G26" s="22"/>
       <c r="H26" s="22"/>
@@ -32213,9 +32215,9 @@
     <row r="27" spans="1:26" ht="15.75">
       <c r="A27" s="69"/>
       <c r="B27" s="69"/>
-      <c r="C27" s="155"/>
-      <c r="D27" s="155"/>
-      <c r="E27" s="155"/>
+      <c r="C27" s="157"/>
+      <c r="D27" s="157"/>
+      <c r="E27" s="157"/>
       <c r="F27" s="22"/>
       <c r="G27" s="22"/>
       <c r="H27" s="22"/>
@@ -32241,9 +32243,9 @@
     <row r="28" spans="1:26" ht="15.75">
       <c r="A28" s="69"/>
       <c r="B28" s="69"/>
-      <c r="C28" s="155"/>
-      <c r="D28" s="155"/>
-      <c r="E28" s="155"/>
+      <c r="C28" s="157"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="157"/>
       <c r="F28" s="22"/>
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
@@ -32269,9 +32271,9 @@
     <row r="29" spans="1:26" ht="15.75">
       <c r="A29" s="69"/>
       <c r="B29" s="69"/>
-      <c r="C29" s="155"/>
-      <c r="D29" s="155"/>
-      <c r="E29" s="155"/>
+      <c r="C29" s="157"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="157"/>
       <c r="F29" s="22"/>
       <c r="G29" s="22"/>
       <c r="H29" s="22"/>
@@ -32297,9 +32299,9 @@
     <row r="30" spans="1:26" ht="15.75">
       <c r="A30" s="69"/>
       <c r="B30" s="69"/>
-      <c r="C30" s="155"/>
-      <c r="D30" s="155"/>
-      <c r="E30" s="155"/>
+      <c r="C30" s="157"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="157"/>
       <c r="F30" s="22"/>
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
@@ -32325,9 +32327,9 @@
     <row r="31" spans="1:26" ht="15.75">
       <c r="A31" s="69"/>
       <c r="B31" s="69"/>
-      <c r="C31" s="155"/>
-      <c r="D31" s="155"/>
-      <c r="E31" s="155"/>
+      <c r="C31" s="157"/>
+      <c r="D31" s="157"/>
+      <c r="E31" s="157"/>
       <c r="F31" s="22"/>
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
@@ -32353,9 +32355,9 @@
     <row r="32" spans="1:26" ht="15.75">
       <c r="A32" s="69"/>
       <c r="B32" s="69"/>
-      <c r="C32" s="155"/>
-      <c r="D32" s="155"/>
-      <c r="E32" s="155"/>
+      <c r="C32" s="157"/>
+      <c r="D32" s="157"/>
+      <c r="E32" s="157"/>
       <c r="F32" s="22"/>
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
@@ -32381,9 +32383,9 @@
     <row r="33" spans="1:26" ht="15.75">
       <c r="A33" s="69"/>
       <c r="B33" s="69"/>
-      <c r="C33" s="155"/>
-      <c r="D33" s="155"/>
-      <c r="E33" s="155"/>
+      <c r="C33" s="157"/>
+      <c r="D33" s="157"/>
+      <c r="E33" s="157"/>
       <c r="F33" s="22"/>
       <c r="G33" s="22"/>
       <c r="H33" s="22"/>
@@ -32409,9 +32411,9 @@
     <row r="34" spans="1:26" ht="15.75">
       <c r="A34" s="69"/>
       <c r="B34" s="69"/>
-      <c r="C34" s="155"/>
-      <c r="D34" s="155"/>
-      <c r="E34" s="155"/>
+      <c r="C34" s="157"/>
+      <c r="D34" s="157"/>
+      <c r="E34" s="157"/>
       <c r="F34" s="22"/>
       <c r="G34" s="22"/>
       <c r="H34" s="22"/>
@@ -32437,9 +32439,9 @@
     <row r="35" spans="1:26" ht="15.75">
       <c r="A35" s="69"/>
       <c r="B35" s="69"/>
-      <c r="C35" s="155"/>
-      <c r="D35" s="155"/>
-      <c r="E35" s="155"/>
+      <c r="C35" s="157"/>
+      <c r="D35" s="157"/>
+      <c r="E35" s="157"/>
       <c r="F35" s="22"/>
       <c r="G35" s="22"/>
       <c r="H35" s="22"/>
@@ -32465,9 +32467,9 @@
     <row r="36" spans="1:26" ht="15.75">
       <c r="A36" s="69"/>
       <c r="B36" s="69"/>
-      <c r="C36" s="155"/>
-      <c r="D36" s="155"/>
-      <c r="E36" s="155"/>
+      <c r="C36" s="157"/>
+      <c r="D36" s="157"/>
+      <c r="E36" s="157"/>
       <c r="F36" s="22"/>
       <c r="G36" s="22"/>
       <c r="H36" s="22"/>
@@ -32493,9 +32495,9 @@
     <row r="37" spans="1:26" ht="15.75">
       <c r="A37" s="69"/>
       <c r="B37" s="69"/>
-      <c r="C37" s="155"/>
-      <c r="D37" s="155"/>
-      <c r="E37" s="155"/>
+      <c r="C37" s="157"/>
+      <c r="D37" s="157"/>
+      <c r="E37" s="157"/>
       <c r="F37" s="22"/>
       <c r="G37" s="22"/>
       <c r="H37" s="22"/>
@@ -32521,9 +32523,9 @@
     <row r="38" spans="1:26" ht="15.75">
       <c r="A38" s="69"/>
       <c r="B38" s="69"/>
-      <c r="C38" s="155"/>
-      <c r="D38" s="155"/>
-      <c r="E38" s="155"/>
+      <c r="C38" s="157"/>
+      <c r="D38" s="157"/>
+      <c r="E38" s="157"/>
       <c r="F38" s="22"/>
       <c r="G38" s="22"/>
       <c r="H38" s="22"/>
@@ -32549,9 +32551,9 @@
     <row r="39" spans="1:26" ht="15.75">
       <c r="A39" s="69"/>
       <c r="B39" s="69"/>
-      <c r="C39" s="155"/>
-      <c r="D39" s="155"/>
-      <c r="E39" s="155"/>
+      <c r="C39" s="157"/>
+      <c r="D39" s="157"/>
+      <c r="E39" s="157"/>
       <c r="F39" s="22"/>
       <c r="G39" s="22"/>
       <c r="H39" s="22"/>
@@ -32604,36 +32606,6 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="C31:E31"/>
     <mergeCell ref="C37:E37"/>
     <mergeCell ref="C38:E38"/>
     <mergeCell ref="C39:E39"/>
@@ -32642,6 +32614,36 @@
     <mergeCell ref="C34:E34"/>
     <mergeCell ref="C35:E35"/>
     <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -32723,10 +32725,10 @@
       <c r="C2" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D2" s="159" t="s">
+      <c r="D2" s="158" t="s">
         <v>102</v>
       </c>
-      <c r="E2" s="159"/>
+      <c r="E2" s="158"/>
       <c r="F2" s="1" t="s">
         <v>92</v>
       </c>
@@ -32761,10 +32763,10 @@
       <c r="C3" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="160" t="s">
+      <c r="D3" s="159" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="160"/>
+      <c r="E3" s="159"/>
       <c r="F3" s="71" t="s">
         <v>1</v>
       </c>
@@ -32796,8 +32798,8 @@
       <c r="B4" s="62">
         <v>1.08</v>
       </c>
-      <c r="D4" s="158"/>
-      <c r="E4" s="158"/>
+      <c r="D4" s="160"/>
+      <c r="E4" s="160"/>
       <c r="F4" s="6" t="s">
         <v>328</v>
       </c>
@@ -32830,8 +32832,8 @@
         <f>A5+0.16</f>
         <v>1.24</v>
       </c>
-      <c r="D5" s="158"/>
-      <c r="E5" s="158"/>
+      <c r="D5" s="160"/>
+      <c r="E5" s="160"/>
       <c r="F5" s="6" t="s">
         <v>327</v>
       </c>
@@ -32860,10 +32862,10 @@
       <c r="B6" s="6">
         <v>0.21</v>
       </c>
-      <c r="D6" s="158" t="s">
+      <c r="D6" s="160" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="158"/>
+      <c r="E6" s="160"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
@@ -32890,10 +32892,10 @@
         <v>0.49</v>
       </c>
       <c r="C7"/>
-      <c r="D7" s="158" t="s">
+      <c r="D7" s="160" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="158"/>
+      <c r="E7" s="160"/>
       <c r="F7"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
@@ -32921,10 +32923,10 @@
       <c r="B8" s="6">
         <v>0.87</v>
       </c>
-      <c r="D8" s="158" t="s">
+      <c r="D8" s="160" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="158"/>
+      <c r="E8" s="160"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
@@ -32948,8 +32950,8 @@
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="62"/>
-      <c r="D9" s="158"/>
-      <c r="E9" s="158"/>
+      <c r="D9" s="160"/>
+      <c r="E9" s="160"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
@@ -32973,8 +32975,8 @@
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="62"/>
-      <c r="D10" s="158"/>
-      <c r="E10" s="158"/>
+      <c r="D10" s="160"/>
+      <c r="E10" s="160"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
@@ -32998,8 +33000,8 @@
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="62"/>
-      <c r="D11" s="158"/>
-      <c r="E11" s="158"/>
+      <c r="D11" s="160"/>
+      <c r="E11" s="160"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
@@ -33023,8 +33025,8 @@
     </row>
     <row r="12" spans="1:26">
       <c r="A12" s="62"/>
-      <c r="D12" s="158"/>
-      <c r="E12" s="158"/>
+      <c r="D12" s="160"/>
+      <c r="E12" s="160"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
@@ -33048,8 +33050,8 @@
     </row>
     <row r="13" spans="1:26">
       <c r="A13" s="62"/>
-      <c r="D13" s="158"/>
-      <c r="E13" s="158"/>
+      <c r="D13" s="160"/>
+      <c r="E13" s="160"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
@@ -33098,8 +33100,8 @@
     </row>
     <row r="15" spans="1:26">
       <c r="A15" s="62"/>
-      <c r="D15" s="158"/>
-      <c r="E15" s="158"/>
+      <c r="D15" s="160"/>
+      <c r="E15" s="160"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
@@ -33128,8 +33130,8 @@
       <c r="B16" s="6">
         <v>0.12</v>
       </c>
-      <c r="D16" s="158"/>
-      <c r="E16" s="158"/>
+      <c r="D16" s="160"/>
+      <c r="E16" s="160"/>
       <c r="F16" s="6" t="s">
         <v>336</v>
       </c>
@@ -33161,8 +33163,8 @@
       <c r="B17" s="6">
         <v>0.21</v>
       </c>
-      <c r="D17" s="158"/>
-      <c r="E17" s="158"/>
+      <c r="D17" s="160"/>
+      <c r="E17" s="160"/>
       <c r="F17" s="6" t="s">
         <v>337</v>
       </c>
@@ -33194,8 +33196,8 @@
       <c r="B18" s="6">
         <v>0.33</v>
       </c>
-      <c r="D18" s="158"/>
-      <c r="E18" s="158"/>
+      <c r="D18" s="160"/>
+      <c r="E18" s="160"/>
       <c r="F18" s="6" t="s">
         <v>338</v>
       </c>
@@ -33227,8 +33229,8 @@
       <c r="B19" s="6">
         <v>0.45</v>
       </c>
-      <c r="D19" s="158"/>
-      <c r="E19" s="158"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="160"/>
       <c r="F19" s="6" t="s">
         <v>339</v>
       </c>
@@ -33260,8 +33262,8 @@
       <c r="B20" s="6">
         <v>0.63</v>
       </c>
-      <c r="D20" s="158"/>
-      <c r="E20" s="158"/>
+      <c r="D20" s="160"/>
+      <c r="E20" s="160"/>
       <c r="F20" s="6" t="s">
         <v>340</v>
       </c>
@@ -33293,8 +33295,8 @@
       <c r="B21" s="6">
         <v>0.75</v>
       </c>
-      <c r="D21" s="158"/>
-      <c r="E21" s="158"/>
+      <c r="D21" s="160"/>
+      <c r="E21" s="160"/>
       <c r="F21" s="6" t="s">
         <v>341</v>
       </c>
@@ -33326,8 +33328,8 @@
       <c r="B22" s="6">
         <v>0.87</v>
       </c>
-      <c r="D22" s="158"/>
-      <c r="E22" s="158"/>
+      <c r="D22" s="160"/>
+      <c r="E22" s="160"/>
       <c r="F22" s="6" t="s">
         <v>342</v>
       </c>
@@ -33359,8 +33361,8 @@
       <c r="B23" s="6">
         <v>0.99</v>
       </c>
-      <c r="D23" s="158"/>
-      <c r="E23" s="158"/>
+      <c r="D23" s="160"/>
+      <c r="E23" s="160"/>
       <c r="F23" s="6" t="s">
         <v>343</v>
       </c>
@@ -33392,8 +33394,8 @@
       <c r="B24" s="6">
         <v>1.08</v>
       </c>
-      <c r="D24" s="158"/>
-      <c r="E24" s="158"/>
+      <c r="D24" s="160"/>
+      <c r="E24" s="160"/>
       <c r="F24" s="6" t="s">
         <v>344</v>
       </c>
@@ -33425,8 +33427,8 @@
       <c r="B25" s="6">
         <v>1.24</v>
       </c>
-      <c r="D25" s="158"/>
-      <c r="E25" s="158"/>
+      <c r="D25" s="160"/>
+      <c r="E25" s="160"/>
       <c r="F25" s="6" t="s">
         <v>345</v>
       </c>
@@ -33453,8 +33455,8 @@
     </row>
     <row r="26" spans="1:26">
       <c r="A26" s="62"/>
-      <c r="D26" s="158"/>
-      <c r="E26" s="158"/>
+      <c r="D26" s="160"/>
+      <c r="E26" s="160"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
@@ -33479,8 +33481,8 @@
     <row r="27" spans="1:26">
       <c r="A27" s="62"/>
       <c r="B27" s="62"/>
-      <c r="D27" s="158"/>
-      <c r="E27" s="158"/>
+      <c r="D27" s="160"/>
+      <c r="E27" s="160"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
@@ -33504,8 +33506,8 @@
     </row>
     <row r="28" spans="1:26">
       <c r="A28" s="62"/>
-      <c r="D28" s="158"/>
-      <c r="E28" s="158"/>
+      <c r="D28" s="160"/>
+      <c r="E28" s="160"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
@@ -33531,8 +33533,8 @@
       <c r="A29" s="62"/>
       <c r="B29" s="59"/>
       <c r="C29" s="59"/>
-      <c r="D29" s="158"/>
-      <c r="E29" s="158"/>
+      <c r="D29" s="160"/>
+      <c r="E29" s="160"/>
       <c r="F29" s="59"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
@@ -33559,8 +33561,8 @@
       <c r="A30" s="62"/>
       <c r="B30" s="59"/>
       <c r="C30" s="59"/>
-      <c r="D30" s="158"/>
-      <c r="E30" s="158"/>
+      <c r="D30" s="160"/>
+      <c r="E30" s="160"/>
       <c r="F30" s="59"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -33585,8 +33587,8 @@
     </row>
     <row r="31" spans="1:26">
       <c r="A31" s="62"/>
-      <c r="D31" s="158"/>
-      <c r="E31" s="158"/>
+      <c r="D31" s="160"/>
+      <c r="E31" s="160"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
@@ -33610,8 +33612,8 @@
     </row>
     <row r="32" spans="1:26">
       <c r="A32" s="62"/>
-      <c r="D32" s="158"/>
-      <c r="E32" s="158"/>
+      <c r="D32" s="160"/>
+      <c r="E32" s="160"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
@@ -33635,8 +33637,8 @@
     </row>
     <row r="33" spans="1:26">
       <c r="A33" s="62"/>
-      <c r="D33" s="158"/>
-      <c r="E33" s="158"/>
+      <c r="D33" s="160"/>
+      <c r="E33" s="160"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
       <c r="I33" s="9"/>
@@ -33660,8 +33662,8 @@
     </row>
     <row r="34" spans="1:26">
       <c r="A34" s="62"/>
-      <c r="D34" s="158"/>
-      <c r="E34" s="158"/>
+      <c r="D34" s="160"/>
+      <c r="E34" s="160"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
       <c r="I34" s="9"/>
@@ -33685,8 +33687,8 @@
     </row>
     <row r="35" spans="1:26">
       <c r="A35" s="62"/>
-      <c r="D35" s="158"/>
-      <c r="E35" s="158"/>
+      <c r="D35" s="160"/>
+      <c r="E35" s="160"/>
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
@@ -33710,8 +33712,8 @@
     </row>
     <row r="36" spans="1:26">
       <c r="A36" s="62"/>
-      <c r="D36" s="158"/>
-      <c r="E36" s="158"/>
+      <c r="D36" s="160"/>
+      <c r="E36" s="160"/>
       <c r="G36" s="9"/>
       <c r="H36" s="9"/>
       <c r="I36" s="9"/>
@@ -33735,8 +33737,8 @@
     </row>
     <row r="37" spans="1:26">
       <c r="A37" s="62"/>
-      <c r="D37" s="158"/>
-      <c r="E37" s="158"/>
+      <c r="D37" s="160"/>
+      <c r="E37" s="160"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
@@ -33760,8 +33762,8 @@
     </row>
     <row r="38" spans="1:26">
       <c r="A38" s="62"/>
-      <c r="D38" s="158"/>
-      <c r="E38" s="158"/>
+      <c r="D38" s="160"/>
+      <c r="E38" s="160"/>
       <c r="G38" s="9"/>
       <c r="H38" s="9"/>
       <c r="I38" s="9"/>
@@ -33785,8 +33787,8 @@
     </row>
     <row r="39" spans="1:26">
       <c r="A39" s="62"/>
-      <c r="D39" s="158"/>
-      <c r="E39" s="158"/>
+      <c r="D39" s="160"/>
+      <c r="E39" s="160"/>
       <c r="G39" s="9"/>
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
@@ -33810,8 +33812,8 @@
     </row>
     <row r="40" spans="1:26">
       <c r="A40" s="62"/>
-      <c r="D40" s="158"/>
-      <c r="E40" s="158"/>
+      <c r="D40" s="160"/>
+      <c r="E40" s="160"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
       <c r="I40" s="9"/>
@@ -33835,8 +33837,8 @@
     </row>
     <row r="41" spans="1:26">
       <c r="A41" s="62"/>
-      <c r="D41" s="158"/>
-      <c r="E41" s="158"/>
+      <c r="D41" s="160"/>
+      <c r="E41" s="160"/>
       <c r="G41" s="9"/>
       <c r="H41" s="9"/>
       <c r="I41" s="9"/>
@@ -33860,8 +33862,8 @@
     </row>
     <row r="42" spans="1:26">
       <c r="A42" s="62"/>
-      <c r="D42" s="158"/>
-      <c r="E42" s="158"/>
+      <c r="D42" s="160"/>
+      <c r="E42" s="160"/>
       <c r="G42" s="9"/>
       <c r="H42" s="9"/>
       <c r="I42" s="9"/>
@@ -33885,8 +33887,8 @@
     </row>
     <row r="43" spans="1:26">
       <c r="A43" s="62"/>
-      <c r="D43" s="158"/>
-      <c r="E43" s="158"/>
+      <c r="D43" s="160"/>
+      <c r="E43" s="160"/>
       <c r="G43" s="9"/>
       <c r="H43" s="9"/>
       <c r="I43" s="9"/>
@@ -33910,8 +33912,8 @@
     </row>
     <row r="44" spans="1:26">
       <c r="A44" s="62"/>
-      <c r="D44" s="158"/>
-      <c r="E44" s="158"/>
+      <c r="D44" s="160"/>
+      <c r="E44" s="160"/>
       <c r="G44" s="9"/>
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
@@ -33935,8 +33937,8 @@
     </row>
     <row r="45" spans="1:26">
       <c r="A45" s="62"/>
-      <c r="D45" s="158"/>
-      <c r="E45" s="158"/>
+      <c r="D45" s="160"/>
+      <c r="E45" s="160"/>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
       <c r="I45" s="9"/>
@@ -33960,8 +33962,8 @@
     </row>
     <row r="46" spans="1:26">
       <c r="A46" s="62"/>
-      <c r="D46" s="158"/>
-      <c r="E46" s="158"/>
+      <c r="D46" s="160"/>
+      <c r="E46" s="160"/>
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
       <c r="I46" s="9"/>
@@ -33985,8 +33987,8 @@
     </row>
     <row r="47" spans="1:26">
       <c r="A47" s="62"/>
-      <c r="D47" s="158"/>
-      <c r="E47" s="158"/>
+      <c r="D47" s="160"/>
+      <c r="E47" s="160"/>
       <c r="G47" s="9"/>
       <c r="H47" s="9"/>
       <c r="I47" s="9"/>
@@ -34010,8 +34012,8 @@
     </row>
     <row r="48" spans="1:26">
       <c r="A48" s="62"/>
-      <c r="D48" s="158"/>
-      <c r="E48" s="158"/>
+      <c r="D48" s="160"/>
+      <c r="E48" s="160"/>
       <c r="G48" s="9"/>
       <c r="H48" s="9"/>
       <c r="I48" s="9"/>
@@ -34035,8 +34037,8 @@
     </row>
     <row r="49" spans="1:26">
       <c r="A49" s="62"/>
-      <c r="D49" s="158"/>
-      <c r="E49" s="158"/>
+      <c r="D49" s="160"/>
+      <c r="E49" s="160"/>
       <c r="G49" s="9"/>
       <c r="H49" s="9"/>
       <c r="I49" s="9"/>
@@ -34088,38 +34090,6 @@
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="D50:E50"/>
@@ -34136,6 +34106,38 @@
     <mergeCell ref="D35:E35"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{00000000-0002-0000-0400-000000000000}">
@@ -36692,58 +36694,58 @@
       <c r="E2" s="58" t="s">
         <v>118</v>
       </c>
-      <c r="F2" s="163" t="s">
+      <c r="F2" s="161" t="s">
         <v>119</v>
       </c>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163" t="s">
+      <c r="G2" s="161"/>
+      <c r="H2" s="161" t="s">
         <v>120</v>
       </c>
-      <c r="I2" s="163"/>
-      <c r="J2" s="164" t="s">
+      <c r="I2" s="161"/>
+      <c r="J2" s="162" t="s">
         <v>121</v>
       </c>
-      <c r="K2" s="164"/>
-      <c r="L2" s="163" t="s">
+      <c r="K2" s="162"/>
+      <c r="L2" s="161" t="s">
         <v>122</v>
       </c>
-      <c r="M2" s="163"/>
-      <c r="N2" s="164" t="s">
+      <c r="M2" s="161"/>
+      <c r="N2" s="162" t="s">
         <v>123</v>
       </c>
-      <c r="O2" s="164"/>
-      <c r="P2" s="162" t="s">
+      <c r="O2" s="162"/>
+      <c r="P2" s="164" t="s">
         <v>124</v>
       </c>
-      <c r="Q2" s="162"/>
-      <c r="R2" s="159" t="s">
+      <c r="Q2" s="164"/>
+      <c r="R2" s="158" t="s">
         <v>125</v>
       </c>
-      <c r="S2" s="159"/>
-      <c r="T2" s="162" t="s">
+      <c r="S2" s="158"/>
+      <c r="T2" s="164" t="s">
         <v>126</v>
       </c>
-      <c r="U2" s="162"/>
-      <c r="V2" s="159" t="s">
+      <c r="U2" s="164"/>
+      <c r="V2" s="158" t="s">
         <v>127</v>
       </c>
-      <c r="W2" s="159"/>
-      <c r="X2" s="162" t="s">
+      <c r="W2" s="158"/>
+      <c r="X2" s="164" t="s">
         <v>128</v>
       </c>
-      <c r="Y2" s="162"/>
-      <c r="Z2" s="161" t="s">
+      <c r="Y2" s="164"/>
+      <c r="Z2" s="163" t="s">
         <v>129</v>
       </c>
-      <c r="AA2" s="161"/>
-      <c r="AB2" s="161" t="s">
+      <c r="AA2" s="163"/>
+      <c r="AB2" s="163" t="s">
         <v>130</v>
       </c>
-      <c r="AC2" s="161"/>
-      <c r="AD2" s="162" t="s">
+      <c r="AC2" s="163"/>
+      <c r="AD2" s="164" t="s">
         <v>131</v>
       </c>
-      <c r="AE2" s="162"/>
+      <c r="AE2" s="164"/>
       <c r="AF2" s="58" t="s">
         <v>92</v>
       </c>
@@ -38114,11 +38116,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
     <mergeCell ref="Z2:AA2"/>
     <mergeCell ref="AB2:AC2"/>
     <mergeCell ref="AD2:AE2"/>
@@ -38127,6 +38124,11 @@
     <mergeCell ref="T2:U2"/>
     <mergeCell ref="V2:W2"/>
     <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{00000000-0002-0000-0700-000000000000}">
